--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="72">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,28 +37,196 @@
     <t>url</t>
   </si>
   <si>
+    <t>ca/en.report.json</t>
+  </si>
+  <si>
+    <t>["carousel","teaser","teaser","teaser","teaser","teaser","cards","cards"]</t>
+  </si>
+  <si>
+    <t>ca/en</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:25:30.547Z</t>
+  </si>
+  <si>
+    <t>WKND Adventures and Travel</t>
+  </si>
+  <si>
+    <t>https://wknd.site/ca/en.html</t>
+  </si>
+  <si>
+    <t>ca/fr.report.json</t>
+  </si>
+  <si>
+    <t>["teaser"]</t>
+  </si>
+  <si>
+    <t>ca/fr</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:27:30.527Z</t>
+  </si>
+  <si>
+    <t>Français</t>
+  </si>
+  <si>
+    <t>https://wknd.site/ca/fr.html</t>
+  </si>
+  <si>
+    <t>ch/de.report.json</t>
+  </si>
+  <si>
+    <t>ch/de</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:27:36.646Z</t>
+  </si>
+  <si>
+    <t>Deutsch</t>
+  </si>
+  <si>
+    <t>https://wknd.site/ch/de.html</t>
+  </si>
+  <si>
+    <t>ch/fr.report.json</t>
+  </si>
+  <si>
+    <t>ch/fr</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:27:43.144Z</t>
+  </si>
+  <si>
+    <t>https://wknd.site/ch/fr.html</t>
+  </si>
+  <si>
+    <t>ch/it.report.json</t>
+  </si>
+  <si>
+    <t>ch/it</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:27:48.003Z</t>
+  </si>
+  <si>
+    <t>Italiano</t>
+  </si>
+  <si>
+    <t>https://wknd.site/ch/it.html</t>
+  </si>
+  <si>
+    <t>de/de.report.json</t>
+  </si>
+  <si>
+    <t>de/de</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:25:34.232Z</t>
+  </si>
+  <si>
+    <t>https://wknd.site/de/de.html</t>
+  </si>
+  <si>
+    <t>es/es.report.json</t>
+  </si>
+  <si>
+    <t>es/es</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:27:54.404Z</t>
+  </si>
+  <si>
+    <t>Español</t>
+  </si>
+  <si>
+    <t>https://wknd.site/es/es.html</t>
+  </si>
+  <si>
+    <t>fr/fr.report.json</t>
+  </si>
+  <si>
+    <t>fr/fr</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:28:00.254Z</t>
+  </si>
+  <si>
+    <t>https://wknd.site/fr/fr.html</t>
+  </si>
+  <si>
+    <t>it/it.report.json</t>
+  </si>
+  <si>
+    <t>it/it</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:28:03.998Z</t>
+  </si>
+  <si>
+    <t>https://wknd.site/it/it.html</t>
+  </si>
+  <si>
     <t>us/en.report.json</t>
   </si>
   <si>
-    <t>["carousel","teaser","teaser","teaser","teaser","teaser","cards","cards"]</t>
-  </si>
-  <si>
     <t>us/en</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>home</t>
-  </si>
-  <si>
-    <t>2026-09-07T18:31:45.698Z</t>
-  </si>
-  <si>
-    <t>WKND Adventures and Travel</t>
+    <t>2026-09-10T17:25:24.904Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en.html</t>
+  </si>
+  <si>
+    <t>us/es.report.json</t>
+  </si>
+  <si>
+    <t>us/es</t>
+  </si>
+  <si>
+    <t>2026-09-10T17:28:08.519Z</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/es.html</t>
+  </si>
+  <si>
+    <t>ca/en/faqs.report.json</t>
+  </si>
+  <si>
+    <t>["hero","accordion","accordion"]</t>
+  </si>
+  <si>
+    <t>ca/en/faqs</t>
+  </si>
+  <si>
+    <t>faq</t>
+  </si>
+  <si>
+    <t>2026-09-10T16:45:35.270Z</t>
+  </si>
+  <si>
+    <t>FAQs</t>
+  </si>
+  <si>
+    <t>https://wknd.site/ca/en/faqs.html</t>
+  </si>
+  <si>
+    <t>us/en/faqs.report.json</t>
+  </si>
+  <si>
+    <t>us/en/faqs</t>
+  </si>
+  <si>
+    <t>2026-09-10T16:45:41.158Z</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/faqs.html</t>
   </si>
 </sst>
 </file>
@@ -447,16 +615,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="8" max="8" width="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +677,318 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
